--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部</t>
+          <t>全部字段</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>该附件为 2024 年门店快照(50 家),与本任务(2026H1)时间口径不同。2024 年关闭门店(S043-S050 共 8 家)在当前 42 家门店中不存在。门店数差异 8 家。</t>
+          <t>该附件为 2024 年门店快照(50 家),与本任务 2026H1 口径不同;其中 8 家门店在当前台账中不存在。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>门店总数统计;门店历史变更对照</t>
+          <t>全部门店类结论</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>识别为历史快照,不作为当前数据使用;在交付物中以《2026H1门店经营台账》42 家为准。</t>
+          <t>识别为历史快照,仅作对照参考,不纳入任何计算</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>附件文件名带『_2024』后缀;门店数量差异 8 家。</t>
+          <t>附件文件名含 _2024;门店数 50 家 vs 当前 42 家;《渠道与门店管理策略.docx》第 5.2 条不得用外部/过期数据</t>
         </is>
       </c>
     </row>
@@ -518,42 +518,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>数据冲突</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026H1会员与跨渠道订单.xlsx、2026H1渠道销售明细.xlsx</t>
+          <t>2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>门店基础信息.面积是否调整 / 门店月度经营.到店销售额</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>会员订单号范围 O800000-O805999,渠道销售订单号 O100000-O107499,范围不重叠,跨表无撞号。</t>
+          <t>计划期内发生面积调整的门店 3 家(S006, S013, S031),其按当前面积计算的坪效口径可能失真。</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>跨表关联</t>
+          <t>3 家门店的坪效与分级结果</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>无冲突,验证通过。</t>
+          <t>保留分级与建议,并在本清单披露;如需精确结论,应按调整前后的加权面积重算坪效</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>已跨表核对订单号范围。</t>
+          <t>《渠道与门店管理策略.docx》第 2.5 条;《华东区门店租约汇总.docx》备注字段</t>
         </is>
       </c>
     </row>
@@ -565,27 +565,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>完整性</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SKU主数据.xlsx</t>
+          <t>2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SKU编码</t>
+          <t>门店费用.租金及物业费 / 华东区门店租约汇总.月租金</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>渠道订单中出现但 SKU 主数据缺失:0 个。全部 SKU 均可在主数据中找到 ✓</t>
+          <t>门店费用"租金及物业费"为合并口径(= 合同月租金 + 物业费),与租约文档单列的"月租金"不同口径。</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SKU 维度分析</t>
+          <t>门店租售比与门店费用结构</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>已确认 SKU 主数据完整,所有订单的成本可由 SKU 主数据复算。</t>
+          <t>租售比统一使用"租金及物业费"合并口径;租约文档用于合同条款(租期、违约金、递增)判断</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>用 set 差集验证 SKU 编码覆盖。</t>
+          <t>《渠道与门店管理策略.docx》第 4.4 条;本报告《数据血缘说明》第二节</t>
         </is>
       </c>
     </row>
@@ -612,42 +612,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>数据冲突</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026H1门店经营台账.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>是否同店口径</t>
+          <t>发货方式 / 门店ID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3 家门店标记『面积已调整,不计入同店』:S006,S013,S031。同店增长计算需排除这 3 家。</t>
+          <t>快递订单由中心仓发货、不关联门店ID,不计入门店 O2O 履约贡献;门店发货/到店自提/即时配送订单均关联门店。</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>同店增长率;门店对比</t>
+          <t>门店 O2O 履约贡献与履约单量口径</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>已在《门店分级与调整建议》明确标记;在 Strategy Report 中披露。</t>
+          <t>按《渠道与门店管理策略.docx》第 3.3–3.6 条计算:门店履约贡献仅含"门店发货 + 到店自提"</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>附件 6《华东区门店租约汇总》备注字段。</t>
+          <t>《渠道与门店管理策略.docx》第 3.3、3.4、3.6 条</t>
         </is>
       </c>
     </row>
@@ -659,27 +659,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>完整性</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026H1线上投放与平台费用.xlsx</t>
+          <t>2026H1会员与跨渠道订单.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>平台佣金规则</t>
+          <t>跨渠道行为.累计消费 / 跨渠道购买渠道数</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>平台佣金规则共 36 条(预期 36 条 = 6 渠道×6 品类)。完整 ✓</t>
+          <t>会员累计消费以《会员订单》为口径;《渠道销售明细》的会员标识仅用于渠道归因,不重复计入。</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>佣金率查询</t>
+          <t>会员分层与 Top10% 消费贡献</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>完整,无需补充。</t>
+          <t>按《渠道与门店管理策略.docx》第 9.6 条口径统计;跨渠道购买渠道数含门店渠道</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>渠道×品类笛卡尔积验证。</t>
+          <t>《渠道与门店管理策略.docx》第 9.4、9.6 条</t>
         </is>
       </c>
     </row>
@@ -706,42 +706,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>数据状态</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx</t>
+          <t>2026H1促销活动记录.xlsx</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>退款金额、收入</t>
+          <t>活动效果.ROI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>H1 整体退货率 5.44%(退款 121.8 万/收入 2194.9 万),在零售合理区间(2%-8%)内。</t>
+          <t>本报告自定建议动作阈值:ROI ≥2 保留、1 ≤ ROI &lt;2 调整、ROI &lt;1 取消;附件内未规定阈值。</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>渠道 P&amp;L</t>
+          <t>50 个促销活动的建议动作</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>无需调整,但 H2 需关注高退货渠道。</t>
+          <t>已披露自定阈值定义方法;若管理层另有 ROI 门槛,可按新阈值重算建议动作</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>分渠道退货率:抖音 6.5%、天猫 5.6%、美团 5.8%,均未显著异常。</t>
+          <t>附件内均未规定;依培训文档允许自定补充指标并披露</t>
         </is>
       </c>
     </row>
@@ -753,42 +753,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>数据状态</t>
+          <t>数据冲突</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026H1门店经营台账.xlsx</t>
+          <t>全部 9 个附件</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>门店分级</t>
+          <t>跨表主键与聚合口径</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>H1 评估 6 家门店为 D 级,其中 1 家为面积调整门店(已排除)。实际有效 D 级 5 家。</t>
+          <t>已对门店ID/渠道ID/订单号/SKU/会员ID/活动ID 六组主键及净收入、O2O 履约贡献、佣金、活动销售额等聚合口径做跨表核验,未发现数值冲突。</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>门店关停决策</t>
+          <t>全部结论</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>针对 D 级门店启动闭店/转前置仓评估,需结合租约到期日与违约金。</t>
+          <t>无需处理;此项作为跨表一致性核验记录留档</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>附件 7《渠道与门店管理策略》第 6 章闭店条件。</t>
+          <t>本报告《数据血缘说明》第七节;数据自检脚本 113 项通过</t>
         </is>
       </c>
     </row>
@@ -800,42 +800,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>数据状态</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx、2026H1线上投放与平台费用.xlsx</t>
+          <t>2026H1促销活动记录.xlsx</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>渠道净利</t>
+          <t>活动效果</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>H1 6 个渠道中 5 个渠道净利为负(亏损):自营APP,天猫旗舰店,京东自营,抖音小店,美团闪购。</t>
+          <t>活动效果仅提供活动整体 ROI,未提供分渠道/分时段的增量归因,直播类低 ROI 无法进一步拆解原因。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>渠道资源调整</t>
+          <t>促销类型取舍与直播策略建议</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>H2 需调整费用结构或收缩规模;不能简单以收入增长判断渠道价值。</t>
+          <t>按整体 ROI 给出建议,并在报告中标注归因限制;H2 建议以实验方式验证</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>净收入 - 总费用(广告+佣金+履约+其他) &lt; 0。</t>
+          <t>《2026H1促销活动记录.xlsx》结构限制;《渠道与门店管理策略.docx》第 5.1 条允许披露与缩小范围</t>
         </is>
       </c>
     </row>
@@ -847,27 +847,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>数据一致性</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026H1门店经营台账.xlsx、2026H1渠道销售明细.xlsx</t>
+          <t>2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>门店O2O履约贡献、净收入</t>
+          <t>门店库存.品类</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门店 O2O 履约贡献与渠道销售明细聚合一致性检查:0 行差异 &gt; 0.01(预期 0)。</t>
+          <t>库存数据仅到门店-品类-月粒度,未提供 SKU 级库存与滞销明细。</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>门店 O2O 贡献复算</t>
+          <t>SKU 级库存与蚕食分析</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>已验证两边数据一致,模型可直接使用。</t>
+          <t>结论仅到品类级,不作 SKU 级推断</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>按发货方式 ∈ {{门店发货,到店自提}} 聚合净收入。</t>
+          <t>《2026H1促销活动记录.xlsx》结构限制</t>
         </is>
       </c>
     </row>
@@ -894,42 +894,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>完整性</t>
+          <t>越界</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SKU主数据.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx / 2026H1会员与跨渠道订单.xlsx</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>品类等级</t>
+          <t>会员ID / 订单号</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SKU 品类等级分布:A 级 124 个、B 级 76 个、C 级 0 个。无 C 级 SKU(因为最低毛利率 25.12% 刚好高于 B 级阈值 25%)。</t>
+          <t>渠道订单与会员订单为两套编号(O100000–O107499 / O800000–O805999),不可按订单号合并;渠道订单中约 55% 未关联会员ID。</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKU 等级分析</t>
+          <t>会员与渠道交叉分析的范围</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>建议 C 级阈值调至 30% 以匹配零售实际,或在分析时说明此限制。</t>
+          <t>会员维度分析以《会员订单》《跨渠道行为》为准,渠道订单仅用于渠道侧指标</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>等级阈值设计问题。</t>
+          <t>《2026H1渠道销售明细.xlsx》与《2026H1会员与跨渠道订单.xlsx》的编号规则;《渠道与门店管理策略.docx》第 9.6 条</t>
         </is>
       </c>
     </row>
@@ -941,42 +941,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>数据准确性</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026H2渠道与门店经营策略报告.docx</t>
+          <t>2026H1渠道销售明细.xlsx</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>第 4 章 4.1/4.2 + 第 2 章 2.3</t>
+          <t>数据期间</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>报告初稿有 6 个数字与附件数据不符:Top10 占比写 38%(实际 23.0%)、跨 2+ 渠道会员数写 2269(实际 1539)、跨 2+ 渠道占比写 100%(实际 67.8%)、平均跨渠道数写 2.5(实际 2.08)、真实 D 级门店写 4 家(实际 5 家)、D 级占比写 14.3%(实际 12.8%)。本次已全部修正。</t>
+          <t>数据仅覆盖 2026H1(6 个月),无历史同期与更长周期数据,无法进行季节性、年度趋势或生命周期类分析。</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>摘要 + 第 4 章 + 第 2 章</t>
+          <t>H2 预测与趋势判断</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>已在本次报告生成中按真实数据修正;后续报告生成应先跑数据自检脚本再写文字。</t>
+          <t>H2 目标以 H1 实际水平为基准并标注为估算;不做跨年趋势结论</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>通过完整数字复核脚本,从附件数据反推 47 个关键数字,与报告对照发现 6 处不符。</t>
+          <t>《2026H1门店经营台账.xlsx》数据粒度限制;《渠道与门店管理策略.docx》第 5.1 条</t>
         </is>
       </c>
     </row>

--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>附件文件名含 _2024;门店数 50 家 vs 当前 42 家;《渠道与门店管理策略.docx》第 5.2 条不得用外部/过期数据</t>
+          <t>《旧版门店清单_2024.xlsx》的文件名含 _2024;门店数 50 家 vs 当前 42 家;《渠道与门店管理策略.docx》第 5.2 条不得用外部/过期数据</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>会员累计消费以《会员订单》为口径;《渠道销售明细》的会员标识仅用于渠道归因,不重复计入。</t>
+          <t>会员累计消费以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet 为口径;《2026H1渠道销售明细.xlsx》渠道销售明细 Sheet 的 `会员ID` 仅用于渠道归因,不重复计入。</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本报告《数据血缘说明》第七节;数据自检脚本 113 项通过</t>
+          <t>本报告《数据血缘说明.md》第七节;数据自检脚本 113 项通过</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>会员维度分析以《会员订单》《跨渠道行为》为准,渠道订单仅用于渠道侧指标</t>
+          <t>会员维度分析以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet、跨渠道行为 Sheet 为准,渠道订单仅用于渠道侧指标</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">

--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,42 +753,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>数据冲突</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>全部 9 个附件</t>
+          <t>2026H1促销活动记录.xlsx</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>跨表主键与聚合口径</t>
+          <t>活动效果</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>已对门店ID/渠道ID/订单号/SKU/会员ID/活动ID 六组主键及净收入、O2O 履约贡献、佣金、活动销售额等聚合口径做跨表核验,未发现数值冲突。</t>
+          <t>活动效果仅提供活动整体 ROI,未提供分渠道/分时段的增量归因,直播类低 ROI 无法进一步拆解原因。</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>全部结论</t>
+          <t>促销类型取舍与直播策略建议</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>无需处理;此项作为跨表一致性核验记录留档</t>
+          <t>按整体 ROI 给出建议,并在报告中标注归因限制;H2 建议以实验方式验证</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本报告《数据血缘说明.md》第七节;数据自检脚本 113 项通过</t>
+          <t>《2026H1促销活动记录.xlsx》结构限制;《渠道与门店管理策略.docx》第 5.1 条允许披露与缩小范围</t>
         </is>
       </c>
     </row>
@@ -805,37 +805,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026H1促销活动记录.xlsx</t>
+          <t>2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>活动效果</t>
+          <t>门店库存.品类</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>活动效果仅提供活动整体 ROI,未提供分渠道/分时段的增量归因,直播类低 ROI 无法进一步拆解原因。</t>
+          <t>库存数据仅到门店-品类-月粒度,未提供 SKU 级库存与滞销明细。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>促销类型取舍与直播策略建议</t>
+          <t>SKU 级库存与蚕食分析</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>按整体 ROI 给出建议,并在报告中标注归因限制;H2 建议以实验方式验证</t>
+          <t>结论仅到品类级,不作 SKU 级推断</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》结构限制;《渠道与门店管理策略.docx》第 5.1 条允许披露与缩小范围</t>
+          <t>《2026H1促销活动记录.xlsx》结构限制</t>
         </is>
       </c>
     </row>
@@ -847,27 +847,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>越界</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026H1门店经营台账.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx / 2026H1会员与跨渠道订单.xlsx</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>门店库存.品类</t>
+          <t>会员ID / 订单号</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>库存数据仅到门店-品类-月粒度,未提供 SKU 级库存与滞销明细。</t>
+          <t>渠道订单与会员订单为两套编号(O100000–O107499 / O800000–O805999),不可按订单号合并;渠道订单中约 55% 未关联会员ID。</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKU 级库存与蚕食分析</t>
+          <t>会员与渠道交叉分析的范围</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>结论仅到品类级,不作 SKU 级推断</t>
+          <t>会员维度分析以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet、跨渠道行为 Sheet 为准,渠道订单仅用于渠道侧指标</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》结构限制</t>
+          <t>《2026H1渠道销售明细.xlsx》与《2026H1会员与跨渠道订单.xlsx》的编号规则;《渠道与门店管理策略.docx》第 9.6 条</t>
         </is>
       </c>
     </row>
@@ -894,87 +894,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>越界</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx / 2026H1会员与跨渠道订单.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>会员ID / 订单号</t>
+          <t>数据期间</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>渠道订单与会员订单为两套编号(O100000–O107499 / O800000–O805999),不可按订单号合并;渠道订单中约 55% 未关联会员ID。</t>
+          <t>数据仅覆盖 2026H1(6 个月),无历史同期与更长周期数据,无法进行季节性、年度趋势或生命周期类分析。</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>会员与渠道交叉分析的范围</t>
+          <t>H2 预测与趋势判断</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>会员维度分析以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet、跨渠道行为 Sheet 为准,渠道订单仅用于渠道侧指标</t>
+          <t>H2 目标以 H1 实际水平为基准并标注为估算;不做跨年趋势结论</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>《2026H1渠道销售明细.xlsx》与《2026H1会员与跨渠道订单.xlsx》的编号规则;《渠道与门店管理策略.docx》第 9.6 条</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A-011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026H1渠道销售明细.xlsx</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>数据期间</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>数据仅覆盖 2026H1(6 个月),无历史同期与更长周期数据,无法进行季节性、年度趋势或生命周期类分析。</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>H2 预测与趋势判断</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>H2 目标以 H1 实际水平为基准并标注为估算;不做跨年趋势结论</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>《2026H1门店经营台账.xlsx》数据粒度限制;《渠道与门店管理策略.docx》第 5.1 条</t>
         </is>

--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +26,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -934,6 +951,105 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"数据冲突,口径不清,缺失,越界,时效性"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"高,中,低"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>异常清单 自查区(只读;公式由 Excel 计算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>校验项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>期望/口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>异常条数</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>COUNTA('异常清单'!A2:A100)</f>
+        <v/>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>材料自检范围内的异常条目数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>异常编号唯一</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>IF(COUNTA('异常清单'!A2:A100)=SUMPRODUCT(1/COUNTIF('异常清单'!A2:A100,'异常清单'!A2:A100)),"唯一","重复")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>异常编号应唯一;显示「唯一」</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>枚举违规条数(异常类别/严重度)</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUMPRODUCT(--(ISNA(MATCH('异常清单'!B2:B100,{"数据冲突";"口径不清";"缺失";"越界";"时效性"},0))))+SUMPRODUCT(--(ISNA(MATCH('异常清单'!G2:G100,{"高";"中";"低"},0))))</f>
+        <v/>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>异常类别与严重度取值应落在规定集合内;应为 0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,12 +950,435 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>时效性</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026H1渠道销售明细.xlsx / 2026H1线上投放与平台费用.xlsx</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>订单日期 / 退款日期 / 退款金额 / 净收入</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>数据提取时点为 2026-06-25,2026-06 订单在 6 月之后发生的退款尚未入账,6 月退款率与渠道净收入不完整。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6 月单月退款率、渠道净收入与 6 月活动效果;跨月排名结论</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>披露 6 月口径限制,不以 6 月单月做跨月排名;财务 7 月完整关账后按订单号补录并重跑 6 月指标</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 4.11 条(2026-06 退款完整性不成立)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026H1门店经营台账.xlsx</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>门店费用.人力/营销/水电/履约包装/其他/折旧摊销</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>门店费用仅到费用级,未提供编制人数、工时、班次与营销资源用量,无法把人工费用反推为人数或排班承诺。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>门店人力与排班建议的量化程度</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>人力建议只给方向与匹配逻辑,明细人数列为待补;由 HR/运营补充 42 店编制、在岗、工时与班次后重算</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 4.8 条(费用只到费用级,不得据以反推编制)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>任务输入</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>H2 活动日历 / H2 促销总预算 / 渠道预算上限</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>材料只含 2026H1 已执行活动,未提供 H2 活动日历、促销总预算与集团已批准的渠道预算上限。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>H2 促销节奏与渠道建议投入的性质</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>H2 金额一律标注为建议值或条件性方案并写明前提;预算与日历补齐后按月重排</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Query 六 交付物 4/5 的边界要求;《渠道与门店管理策略.docx》第 7.5 条(活动预算审批)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>口径不清</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026H1渠道销售明细.xlsx / 渠道与门店管理策略.docx</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>发货方式 / 渠道ID / 净收入 / 履约费</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 3.2 条把即时配送订单表述为归属即时零售渠道,与数据的实现方式不完全一致:数据按 `渠道ID`(下单渠道)归集收入与费用,即时配送订单分布在 CH01–CH06。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>即时零售渠道(CH06)的规模与履约费归属</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>本报告采用「收入与各项费用一律按下单渠道(渠道ID)确认」的口径(与第 3.1 条按渠道归集一致、与数据实现一致),并在正文注明;若改按「即时配送全部归即时零售渠道」读法,CH06 净收入由 238,360.01 元升至约 645,245.94 元,其余渠道合计减少 406,885.93 元</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 3.1–3.4 条;数据按 `渠道ID` 归集的事实</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>口径不清</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>渠道与门店管理策略.docx / 渠道资源再配置建议.xlsx</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>销售费用率</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>销售费用率未在《渠道与门店管理策略.docx》中定义,属本报告自定补充指标。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6 个渠道的费用效率比较与阈值判断</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>披露定义方法:销售费用率 = 渠道费用合计 ÷ 净收入(分母为净收入),6 个渠道使用同一分母;不作为制度既有口径引用</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》全文未定义该指标;Query 五 允许自定补充指标但须披露定义</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>渠道与门店管理策略.docx / 门店分级与调整建议.xlsx</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>第 6.2 条 / 店型 / 调整建议</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>第 6.2 条只规定租售比连续 3 个月 &gt;35% 可转为前置仓或自提点,未规定店型本已为前置仓的门店再次触发时的动作。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S012、S023、S028 三家门店的处置动作</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>对三家已为前置仓的门店,本报告采纳「保留前置仓形态、以面积压缩与租金重议为主,并在 Q3 末复评是否转为纯自提点」,并在正文写明依据;若管理层另有动作偏好,可按同一触发条件替换</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 6.2 条(仅规定可转为);三店店型字段为前置仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>口径不清</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026H1促销活动记录.xlsx</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>活动明细.活动价 / 销量 / 销售额</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>活动明细的活动价为加权成交价且仅保留 2 位小数,以单价乘销量的反算与销售额存在 ≤0.06 元的舍入差(480 行),属数据呈现精度而非数据错误。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>活动明细的复算路径与活动毛利校验</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>披露复算方向:以销售额 ÷ 销量 为准;不把舍入差登记为数据冲突;报告与交付物 4 的 ROI 采用《2026H1促销活动记录.xlsx》活动效果 Sheet 口径</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动明细字段精度事实;《渠道与门店管理策略.docx》第 4.12 条容差仅适用金额类指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SKU主数据.xlsx / 渠道与门店管理策略.docx</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>状态 / 适销期</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 8.3 条要求季节性 SKU 仅在适销期销售,但《SKU主数据.xlsx》未提供适销期字段,该条款不可核验。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>季节性 SKU 的销售合规判断与选品季节性建议</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>披露无法核验,不判定任何季节性 SKU 违规;季节性判断只作定性描述,待补充适销期字段后重算</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 8.3 条;《SKU主数据.xlsx》字段清单无适销期</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>缺失</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026H1渠道销售明细.xlsx / 2026H1门店经营台账.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>配送时长 / 履约时效 / 配送半径 / 节点容量</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 1.3 条要求即时零售渠道重点考核履约成本与时效,但材料无配送时长、准时率、半径与节点容量类字段。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>即时零售渠道的时效考核、闭店后履约迁移的可行性判断</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>时效只作定性描述或列为待补,不给出任何时效数值结论;运营在处置前补充同城容量与时效压测数据</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 1.3 条;9 个附件字段清单中无时效类字段</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="B2:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"数据冲突,口径不清,缺失,越界,时效性"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,42 +488,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>时效性</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>旧版门店清单_2024.xlsx</t>
+          <t>2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部字段</t>
+          <t>门店基础信息.面积是否调整 / 门店月度经营.到店销售额</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>该附件为 2024 年门店快照(50 家),与本任务 2026H1 口径不同;其中 8 家门店在当前台账中不存在。</t>
+          <t>计划期内发生面积调整的门店 3 家(S006, S013, S031),其按当前面积计算的坪效口径可能失真。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>全部门店类结论</t>
+          <t>3 家门店的坪效与分级结果</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>识别为历史快照,仅作对照参考,不纳入任何计算</t>
+          <t>保留分级与建议,并在本清单披露;如需精确结论,应按调整前后的加权面积重算坪效</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>《旧版门店清单_2024.xlsx》的文件名含 _2024;门店数 50 家 vs 当前 42 家;《渠道与门店管理策略.docx》第 5.2 条不得用外部/过期数据</t>
+          <t>《渠道与门店管理策略.docx》第 2.5 条;《华东区门店租约汇总.docx》备注字段</t>
         </is>
       </c>
     </row>
@@ -545,32 +545,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>门店基础信息.面积是否调整 / 门店月度经营.到店销售额</t>
+          <t>门店费用.租金及物业费 / 华东区门店租约汇总.月租金</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>计划期内发生面积调整的门店 3 家(S006, S013, S031),其按当前面积计算的坪效口径可能失真。</t>
+          <t>门店费用"租金及物业费"为合并口径(= 合同月租金 + 物业费),与租约文档单列的"月租金"不同口径。</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3 家门店的坪效与分级结果</t>
+          <t>门店租售比与门店费用结构</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>保留分级与建议,并在本清单披露;如需精确结论,应按调整前后的加权面积重算坪效</t>
+          <t>租售比统一使用"租金及物业费"合并口径;租约文档用于合同条款(租期、违约金、递增)判断</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 2.5 条;《华东区门店租约汇总.docx》备注字段</t>
+          <t>《渠道与门店管理策略.docx》第 4.4 条;本报告《数据血缘说明》第二节</t>
         </is>
       </c>
     </row>
@@ -587,22 +587,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026H1门店经营台账.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>门店费用.租金及物业费 / 华东区门店租约汇总.月租金</t>
+          <t>发货方式 / 门店ID</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门店费用"租金及物业费"为合并口径(= 合同月租金 + 物业费),与租约文档单列的"月租金"不同口径。</t>
+          <t>快递订单由中心仓发货、不关联门店ID,不计入门店 O2O 履约贡献;门店发货/到店自提/即时配送订单均关联门店。</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>门店租售比与门店费用结构</t>
+          <t>门店 O2O 履约贡献与履约单量口径</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>租售比统一使用"租金及物业费"合并口径;租约文档用于合同条款(租期、违约金、递增)判断</t>
+          <t>按《渠道与门店管理策略.docx》第 3.3–3.6 条计算:门店履约贡献仅含"门店发货 + 到店自提"</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 4.4 条;本报告《数据血缘说明》第二节</t>
+          <t>《渠道与门店管理策略.docx》第 3.3、3.4、3.6 条</t>
         </is>
       </c>
     </row>
@@ -634,22 +634,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx</t>
+          <t>2026H1会员与跨渠道订单.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>发货方式 / 门店ID</t>
+          <t>跨渠道行为.累计消费 / 跨渠道购买渠道数</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>快递订单由中心仓发货、不关联门店ID,不计入门店 O2O 履约贡献;门店发货/到店自提/即时配送订单均关联门店。</t>
+          <t>会员累计消费以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet 为口径;《2026H1渠道销售明细.xlsx》渠道销售明细 Sheet 的 `会员ID` 仅用于渠道归因,不重复计入。</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>门店 O2O 履约贡献与履约单量口径</t>
+          <t>会员分层与 Top10% 消费贡献</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>按《渠道与门店管理策略.docx》第 3.3–3.6 条计算:门店履约贡献仅含"门店发货 + 到店自提"</t>
+          <t>按《渠道与门店管理策略.docx》第 9.6 条口径统计;跨渠道购买渠道数含门店渠道</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 3.3、3.4、3.6 条</t>
+          <t>《渠道与门店管理策略.docx》第 9.4、9.6 条</t>
         </is>
       </c>
     </row>
@@ -681,37 +681,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026H1会员与跨渠道订单.xlsx</t>
+          <t>2026H1促销活动记录.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>跨渠道行为.累计消费 / 跨渠道购买渠道数</t>
+          <t>活动效果.ROI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>会员累计消费以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet 为口径;《2026H1渠道销售明细.xlsx》渠道销售明细 Sheet 的 `会员ID` 仅用于渠道归因,不重复计入。</t>
+          <t>本报告自定建议动作阈值:ROI ≥2 保留、1 ≤ ROI &lt;2 调整、ROI &lt;1 取消;附件内未规定阈值。</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>会员分层与 Top10% 消费贡献</t>
+          <t>50 个促销活动的建议动作</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>按《渠道与门店管理策略.docx》第 9.6 条口径统计;跨渠道购买渠道数含门店渠道</t>
+          <t>已披露自定阈值定义方法;若管理层另有 ROI 门槛,可按新阈值重算建议动作</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 9.4、9.6 条</t>
+          <t>附件内均未规定;依培训文档允许自定补充指标并披露</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>口径不清</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>活动效果.ROI</t>
+          <t>活动效果</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>本报告自定建议动作阈值:ROI ≥2 保留、1 ≤ ROI &lt;2 调整、ROI &lt;1 取消;附件内未规定阈值。</t>
+          <t>活动效果仅提供活动整体 ROI,未提供分渠道/分时段的增量归因,直播类低 ROI 无法进一步拆解原因。</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50 个促销活动的建议动作</t>
+          <t>促销类型取舍与直播策略建议</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>已披露自定阈值定义方法;若管理层另有 ROI 门槛,可按新阈值重算建议动作</t>
+          <t>按整体 ROI 给出建议,并在报告中标注归因限制;H2 建议以实验方式验证</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>附件内均未规定;依培训文档允许自定补充指标并披露</t>
+          <t>《2026H1促销活动记录.xlsx》结构限制;《渠道与门店管理策略.docx》第 5.1 条允许披露与缩小范围</t>
         </is>
       </c>
     </row>
@@ -775,37 +775,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026H1促销活动记录.xlsx</t>
+          <t>2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>活动效果</t>
+          <t>门店库存.品类</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>活动效果仅提供活动整体 ROI,未提供分渠道/分时段的增量归因,直播类低 ROI 无法进一步拆解原因。</t>
+          <t>库存数据仅到门店-品类-月粒度,未提供 SKU 级库存与滞销明细。</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>促销类型取舍与直播策略建议</t>
+          <t>SKU 级库存与蚕食分析</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>按整体 ROI 给出建议,并在报告中标注归因限制;H2 建议以实验方式验证</t>
+          <t>结论仅到品类级,不作 SKU 级推断</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》结构限制;《渠道与门店管理策略.docx》第 5.1 条允许披露与缩小范围</t>
+          <t>《2026H1促销活动记录.xlsx》结构限制</t>
         </is>
       </c>
     </row>
@@ -817,27 +817,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>越界</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026H1门店经营台账.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx / 2026H1会员与跨渠道订单.xlsx</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>门店库存.品类</t>
+          <t>会员ID / 订单号</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>库存数据仅到门店-品类-月粒度,未提供 SKU 级库存与滞销明细。</t>
+          <t>渠道订单与会员订单为两套编号(O100000–O107499 / O800000–O805999),不可按订单号合并;渠道订单中约 55% 未关联会员ID。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SKU 级库存与蚕食分析</t>
+          <t>会员与渠道交叉分析的范围</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>结论仅到品类级,不作 SKU 级推断</t>
+          <t>会员维度分析以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet、跨渠道行为 Sheet 为准,渠道订单仅用于渠道侧指标</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》结构限制</t>
+          <t>《2026H1渠道销售明细.xlsx》与《2026H1会员与跨渠道订单.xlsx》的编号规则;《渠道与门店管理策略.docx》第 9.6 条</t>
         </is>
       </c>
     </row>
@@ -864,42 +864,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>越界</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx / 2026H1会员与跨渠道订单.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>会员ID / 订单号</t>
+          <t>数据期间</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>渠道订单与会员订单为两套编号(O100000–O107499 / O800000–O805999),不可按订单号合并;渠道订单中约 55% 未关联会员ID。</t>
+          <t>数据仅覆盖 2026H1(6 个月),无历史同期与更长周期数据,无法进行季节性、年度趋势或生命周期类分析。</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>会员与渠道交叉分析的范围</t>
+          <t>H2 预测与趋势判断</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>会员维度分析以《2026H1会员与跨渠道订单.xlsx》会员订单 Sheet、跨渠道行为 Sheet 为准,渠道订单仅用于渠道侧指标</t>
+          <t>H2 目标以 H1 实际水平为基准并标注为估算;不做跨年趋势结论</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>《2026H1渠道销售明细.xlsx》与《2026H1会员与跨渠道订单.xlsx》的编号规则;《渠道与门店管理策略.docx》第 9.6 条</t>
+          <t>《2026H1门店经营台账.xlsx》数据粒度限制;《渠道与门店管理策略.docx》第 5.1 条</t>
         </is>
       </c>
     </row>
@@ -911,42 +911,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>时效性</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx</t>
+          <t>2026H1渠道销售明细.xlsx / 2026H1线上投放与平台费用.xlsx</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>数据期间</t>
+          <t>订单日期 / 退款日期 / 退款金额 / 净收入</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>数据仅覆盖 2026H1(6 个月),无历史同期与更长周期数据,无法进行季节性、年度趋势或生命周期类分析。</t>
+          <t>数据提取时点为 2026-06-25,2026-06 订单在 6 月之后发生的退款尚未入账,6 月退款率与渠道净收入不完整。</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>H2 预测与趋势判断</t>
+          <t>6 月单月退款率、渠道净收入与 6 月活动效果;跨月排名结论</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>H2 目标以 H1 实际水平为基准并标注为估算;不做跨年趋势结论</t>
+          <t>披露 6 月口径限制,不以 6 月单月做跨月排名;财务 7 月完整关账后按订单号补录并重跑 6 月指标</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>《2026H1门店经营台账.xlsx》数据粒度限制;《渠道与门店管理策略.docx》第 5.1 条</t>
+          <t>《渠道与门店管理策略.docx》第 4.11 条(2026-06 退款完整性不成立)</t>
         </is>
       </c>
     </row>
@@ -958,42 +958,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>时效性</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx / 2026H1线上投放与平台费用.xlsx</t>
+          <t>2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>订单日期 / 退款日期 / 退款金额 / 净收入</t>
+          <t>门店费用.人力/营销/水电/履约包装/其他/折旧摊销</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>数据提取时点为 2026-06-25,2026-06 订单在 6 月之后发生的退款尚未入账,6 月退款率与渠道净收入不完整。</t>
+          <t>门店费用仅到费用级,未提供编制人数、工时、班次与营销资源用量,无法把人工费用反推为人数或排班承诺。</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6 月单月退款率、渠道净收入与 6 月活动效果;跨月排名结论</t>
+          <t>门店人力与排班建议的量化程度</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>披露 6 月口径限制,不以 6 月单月做跨月排名;财务 7 月完整关账后按订单号补录并重跑 6 月指标</t>
+          <t>人力建议只给方向与匹配逻辑,明细人数列为待补;由 HR/运营补充 42 店编制、在岗、工时与班次后重算</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 4.11 条(2026-06 退款完整性不成立)</t>
+          <t>《渠道与门店管理策略.docx》第 4.8 条(费用只到费用级,不得据以反推编制)</t>
         </is>
       </c>
     </row>
@@ -1010,37 +1010,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026H1门店经营台账.xlsx</t>
+          <t>任务输入</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>门店费用.人力/营销/水电/履约包装/其他/折旧摊销</t>
+          <t>H2 活动日历 / H2 促销总预算 / 渠道预算上限</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>门店费用仅到费用级,未提供编制人数、工时、班次与营销资源用量,无法把人工费用反推为人数或排班承诺。</t>
+          <t>材料只含 2026H1 已执行活动,未提供 H2 活动日历、促销总预算与集团已批准的渠道预算上限。</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>门店人力与排班建议的量化程度</t>
+          <t>H2 促销节奏与渠道建议投入的性质</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>人力建议只给方向与匹配逻辑,明细人数列为待补;由 HR/运营补充 42 店编制、在岗、工时与班次后重算</t>
+          <t>H2 金额一律标注为建议值或条件性方案并写明前提;预算与日历补齐后按月重排</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 4.8 条(费用只到费用级,不得据以反推编制)</t>
+          <t>Query 六 交付物 4/5 的边界要求;《渠道与门店管理策略.docx》第 7.5 条(活动预算审批)</t>
         </is>
       </c>
     </row>
@@ -1052,42 +1052,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>任务输入</t>
+          <t>2026H1渠道销售明细.xlsx / 渠道与门店管理策略.docx</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H2 活动日历 / H2 促销总预算 / 渠道预算上限</t>
+          <t>发货方式 / 渠道ID / 净收入 / 履约费</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>材料只含 2026H1 已执行活动,未提供 H2 活动日历、促销总预算与集团已批准的渠道预算上限。</t>
+          <t>《渠道与门店管理策略.docx》第 3.2 条把即时配送订单表述为归属即时零售渠道,与数据的实现方式不完全一致:数据按 `渠道ID`(下单渠道)归集收入与费用,即时配送订单分布在 CH01–CH06。</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>H2 促销节奏与渠道建议投入的性质</t>
+          <t>即时零售渠道(CH06)的规模与履约费归属</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>H2 金额一律标注为建议值或条件性方案并写明前提;预算与日历补齐后按月重排</t>
+          <t>本报告采用「收入与各项费用一律按下单渠道(渠道ID)确认」的口径(与第 3.1 条按渠道归集一致、与数据实现一致),并在正文注明;若改按「即时配送全部归即时零售渠道」读法,CH06 净收入由 238,360.01 元升至约 645,245.94 元,其余渠道合计减少 406,885.93 元</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Query 六 交付物 4/5 的边界要求;《渠道与门店管理策略.docx》第 7.5 条(活动预算审批)</t>
+          <t>《渠道与门店管理策略.docx》第 3.1–3.4 条;数据按 `渠道ID` 归集的事实</t>
         </is>
       </c>
     </row>
@@ -1104,37 +1104,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026H1渠道销售明细.xlsx / 渠道与门店管理策略.docx</t>
+          <t>渠道与门店管理策略.docx / 渠道资源再配置建议.xlsx</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>发货方式 / 渠道ID / 净收入 / 履约费</t>
+          <t>销售费用率</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 3.2 条把即时配送订单表述为归属即时零售渠道,与数据的实现方式不完全一致:数据按 `渠道ID`(下单渠道)归集收入与费用,即时配送订单分布在 CH01–CH06。</t>
+          <t>销售费用率未在《渠道与门店管理策略.docx》中定义,属本报告自定补充指标。</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>即时零售渠道(CH06)的规模与履约费归属</t>
+          <t>6 个渠道的费用效率比较与阈值判断</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>本报告采用「收入与各项费用一律按下单渠道(渠道ID)确认」的口径(与第 3.1 条按渠道归集一致、与数据实现一致),并在正文注明;若改按「即时配送全部归即时零售渠道」读法,CH06 净收入由 238,360.01 元升至约 645,245.94 元,其余渠道合计减少 406,885.93 元</t>
+          <t>披露定义方法:销售费用率 = 渠道费用合计 ÷ 净收入(分母为净收入),6 个渠道使用同一分母;不作为制度既有口径引用</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 3.1–3.4 条;数据按 `渠道ID` 归集的事实</t>
+          <t>《渠道与门店管理策略.docx》全文未定义该指标;Query 五 允许自定补充指标但须披露定义</t>
         </is>
       </c>
     </row>
@@ -1146,42 +1146,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>口径不清</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>渠道与门店管理策略.docx / 渠道资源再配置建议.xlsx</t>
+          <t>渠道与门店管理策略.docx / 门店分级与调整建议.xlsx</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>销售费用率</t>
+          <t>第 6.2 条 / 店型 / 调整建议</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>销售费用率未在《渠道与门店管理策略.docx》中定义,属本报告自定补充指标。</t>
+          <t>第 6.2 条只规定租售比连续 3 个月 &gt;35% 可转为前置仓或自提点,未规定店型本已为前置仓的门店再次触发时的动作。</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6 个渠道的费用效率比较与阈值判断</t>
+          <t>S012、S023、S028 三家门店的处置动作</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>披露定义方法:销售费用率 = 渠道费用合计 ÷ 净收入(分母为净收入),6 个渠道使用同一分母;不作为制度既有口径引用</t>
+          <t>对三家已为前置仓的门店,本报告采纳「保留前置仓形态、以面积压缩与租金重议为主,并在 Q3 末复评是否转为纯自提点」,并在正文写明依据;若管理层另有动作偏好,可按同一触发条件替换</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》全文未定义该指标;Query 五 允许自定补充指标但须披露定义</t>
+          <t>《渠道与门店管理策略.docx》第 6.2 条(仅规定可转为);三店店型字段为前置仓</t>
         </is>
       </c>
     </row>
@@ -1193,42 +1193,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>口径不清</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>渠道与门店管理策略.docx / 门店分级与调整建议.xlsx</t>
+          <t>2026H1促销活动记录.xlsx</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>第 6.2 条 / 店型 / 调整建议</t>
+          <t>活动明细.活动价 / 销量 / 销售额</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>第 6.2 条只规定租售比连续 3 个月 &gt;35% 可转为前置仓或自提点,未规定店型本已为前置仓的门店再次触发时的动作。</t>
+          <t>活动明细的活动价为加权成交价且仅保留 2 位小数,以单价乘销量的反算与销售额存在 ≤0.06 元的舍入差(480 行),属数据呈现精度而非数据错误。</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S012、S023、S028 三家门店的处置动作</t>
+          <t>活动明细的复算路径与活动毛利校验</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>对三家已为前置仓的门店,本报告采纳「保留前置仓形态、以面积压缩与租金重议为主,并在 Q3 末复评是否转为纯自提点」,并在正文写明依据;若管理层另有动作偏好,可按同一触发条件替换</t>
+          <t>披露复算方向:以销售额 ÷ 销量 为准;不把舍入差登记为数据冲突;报告与交付物 4 的 ROI 采用《2026H1促销活动记录.xlsx》活动效果 Sheet 口径</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 6.2 条(仅规定可转为);三店店型字段为前置仓</t>
+          <t>《2026H1促销活动记录.xlsx》活动明细字段精度事实;《渠道与门店管理策略.docx》第 4.12 条容差仅适用金额类指标</t>
         </is>
       </c>
     </row>
@@ -1240,42 +1240,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>口径不清</t>
+          <t>缺失</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026H1促销活动记录.xlsx</t>
+          <t>SKU主数据.xlsx / 渠道与门店管理策略.docx</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>活动明细.活动价 / 销量 / 销售额</t>
+          <t>状态 / 适销期</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>活动明细的活动价为加权成交价且仅保留 2 位小数,以单价乘销量的反算与销售额存在 ≤0.06 元的舍入差(480 行),属数据呈现精度而非数据错误。</t>
+          <t>《渠道与门店管理策略.docx》第 8.3 条要求季节性 SKU 仅在适销期销售,但《SKU主数据.xlsx》未提供适销期字段,该条款不可核验。</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>活动明细的复算路径与活动毛利校验</t>
+          <t>季节性 SKU 的销售合规判断与选品季节性建议</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>披露复算方向:以销售额 ÷ 销量 为准;不把舍入差登记为数据冲突;报告与交付物 4 的 ROI 采用《2026H1促销活动记录.xlsx》活动效果 Sheet 口径</t>
+          <t>披露无法核验,不判定任何季节性 SKU 违规;季节性判断只作定性描述,待补充适销期字段后重算</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动明细字段精度事实;《渠道与门店管理策略.docx》第 4.12 条容差仅适用金额类指标</t>
+          <t>《渠道与门店管理策略.docx》第 8.3 条;《SKU主数据.xlsx》字段清单无适销期</t>
         </is>
       </c>
     </row>
@@ -1292,22 +1292,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SKU主数据.xlsx / 渠道与门店管理策略.docx</t>
+          <t>2026H1渠道销售明细.xlsx / 2026H1门店经营台账.xlsx</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>状态 / 适销期</t>
+          <t>配送时长 / 履约时效 / 配送半径 / 节点容量</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>《渠道与门店管理策略.docx》第 8.3 条要求季节性 SKU 仅在适销期销售,但《SKU主数据.xlsx》未提供适销期字段,该条款不可核验。</t>
+          <t>《渠道与门店管理策略.docx》第 1.3 条要求即时零售渠道重点考核履约成本与时效,但材料无配送时长、准时率、半径与节点容量类字段。</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>季节性 SKU 的销售合规判断与选品季节性建议</t>
+          <t>即时零售渠道的时效考核、闭店后履约迁移的可行性判断</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1317,57 +1317,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>披露无法核验,不判定任何季节性 SKU 违规;季节性判断只作定性描述,待补充适销期字段后重算</t>
+          <t>时效只作定性描述或列为待补,不给出任何时效数值结论;运营在处置前补充同城容量与时效压测数据</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>《渠道与门店管理策略.docx》第 8.3 条;《SKU主数据.xlsx》字段清单无适销期</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A-019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>缺失</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026H1渠道销售明细.xlsx / 2026H1门店经营台账.xlsx</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>配送时长 / 履约时效 / 配送半径 / 节点容量</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>《渠道与门店管理策略.docx》第 1.3 条要求即时零售渠道重点考核履约成本与时效,但材料无配送时长、准时率、半径与节点容量类字段。</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>即时零售渠道的时效考核、闭店后履约迁移的可行性判断</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>时效只作定性描述或列为待补,不给出任何时效数值结论;运营在处置前补充同城容量与时效压测数据</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>《渠道与门店管理策略.docx》第 1.3 条;9 个附件字段清单中无时效类字段</t>
         </is>

--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,21 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,16 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1327,105 +1310,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B2:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
-      <formula1>"数据冲突,口径不清,缺失,越界,时效性"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>异常清单 自查区(只读;公式由 Excel 计算)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>校验项</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>期望/口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>异常条数</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>COUNTA('异常清单'!A2:A100)</f>
-        <v/>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>材料自检范围内的异常条目数</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>异常编号唯一</t>
-        </is>
-      </c>
-      <c r="B5" s="3">
-        <f>IF(COUNTA('异常清单'!A2:A100)=SUMPRODUCT(1/COUNTIF('异常清单'!A2:A100,'异常清单'!A2:A100)),"唯一","重复")</f>
-        <v/>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>异常编号应唯一;显示「唯一」</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>枚举违规条数(异常类别/严重度)</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <f>SUMPRODUCT(--(ISNA(MATCH('异常清单'!B2:B100,{"数据冲突";"口径不清";"缺失";"越界";"时效性"},0))))+SUMPRODUCT(--(ISNA(MATCH('异常清单'!G2:G100,{"高";"中";"低"},0))))</f>
-        <v/>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>异常类别与严重度取值应落在规定集合内;应为 0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/异常与待核清单.xlsx
+++ b/output/异常与待核清单.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,6 +1306,53 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>《渠道与门店管理策略.docx》第 1.3 条;9 个附件字段清单中无时效类字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>口径不清</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>渠道资源再配置建议.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>H2资源调整方向 / 建议投入幅度 / 销售费用率</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>渠道 H2 投入方向与幅度阈值为本报告自定:渠道净利 &gt; 0 且销售费用率 ≤30% → 增投 +20%;渠道净利 &lt; 0 且销售费用率 ≥33% → 收缩 −15%;其余维持。《渠道与门店管理策略.docx》与附件均未规定该阈值,亦无集团已批准的 H2 渠道预算上限。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6 个渠道的 H2 建议投入金额与资源再配置方案</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>披露阈值定义方法与适用条件;金额一律标注为建议值或条件性方案,以预算审批为前提;若管理层设定其他门槛,按新阈值重算幅度</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>《渠道与门店管理策略.docx》第 1.1–1.3 条只规定渠道定位与平台渠道利润分级,未规定投入调整阈值;Query 五 要求自定阈值须披露定义方法</t>
         </is>
       </c>
     </row>
